--- a/outputs/results/collocations/marker_presence_check_clean_lexical.xlsx
+++ b/outputs/results/collocations/marker_presence_check_clean_lexical.xlsx
@@ -440,10 +440,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>2708</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>5772</v>
       </c>
     </row>
     <row r="3">
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>1665</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>3967</v>
       </c>
     </row>
     <row r="4">
@@ -466,10 +466,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>1943</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="5">
@@ -479,10 +479,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>537</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>692</v>
       </c>
     </row>
     <row r="6">
@@ -518,10 +518,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>262</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>730</v>
       </c>
     </row>
     <row r="9">
@@ -531,10 +531,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>233</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>662</v>
       </c>
     </row>
     <row r="10">
@@ -544,10 +544,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="C10" t="n">
-        <v>1266</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="11">
@@ -583,10 +583,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C13" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
@@ -596,10 +596,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>66</v>
+        <v>157</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>172</v>
       </c>
     </row>
     <row r="15">
